--- a/DS & AI Project - Contentious Subjects Classification.xlsx
+++ b/DS & AI Project - Contentious Subjects Classification.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gregoirebouvier/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/61959a63b48aaa77/Documents/Master/Échange WU vienna/5452_DS-AI_Project_TeamI/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{E486E777-2A1E-B946-93D6-B6D4D8577EC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6800" yWindow="660" windowWidth="21920" windowHeight="16960" xr2:uid="{C0DA9400-01CF-BC47-B4BB-A88E5C5A4DA7}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{C0DA9400-01CF-BC47-B4BB-A88E5C5A4DA7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -470,7 +470,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DC7E1C7-ED0F-374B-BD94-1EEE0FC54CCC}">
   <dimension ref="A2:K11"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="14.6640625" customWidth="1"/>
     <col min="2" max="2" width="31.83203125" customWidth="1"/>
@@ -479,12 +479,12 @@
     <col min="5" max="5" width="24.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:11" ht="24" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A5" s="2" t="s">
         <v>1</v>
       </c>
@@ -509,7 +509,7 @@
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>2</v>
       </c>
@@ -517,27 +517,27 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.4">
       <c r="B7" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.4">
       <c r="B8" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.4">
       <c r="B9" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.4">
       <c r="B10" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.4">
       <c r="B11" t="s">
         <v>13</v>
       </c>
